--- a/output/pdf_financials_xlsx/MLM.xlsx
+++ b/output/pdf_financials_xlsx/MLM.xlsx
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.595037</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.249411</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.142851</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.426745</v>
       </c>
     </row>
     <row r="35">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.595037</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.249411</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.142851</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.426745</v>
       </c>
     </row>
     <row r="37">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/MLM.xlsx
+++ b/output/pdf_financials_xlsx/MLM.xlsx
@@ -547,13 +547,13 @@
         <v>0.7746690000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.840243</v>
+        <v>0.8802450000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.675593</v>
+        <v>0.700244</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.470592</v>
+        <v>0.509292</v>
       </c>
     </row>
     <row r="8">
@@ -5858,7 +5858,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8138,7 +8142,11 @@
           <t>Director fees 11</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
